--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 22-Sep-2026. Built 2026-09-23 09:04 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
         </is>
       </c>
     </row>
@@ -8414,7 +8414,7 @@
         </is>
       </c>
       <c r="P75" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q75" s="9" t="n">
         <v>0</v>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:13 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
         </is>
       </c>
     </row>
@@ -1444,7 +1444,11 @@
       <c r="AB7" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC7" s="4" t="inlineStr"/>
+      <c r="AC7" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1747,7 +1751,11 @@
       <c r="AB10" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC10" s="4" t="inlineStr"/>
+      <c r="AC10" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4215,7 +4223,11 @@
       <c r="AB34" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC34" s="4" t="inlineStr"/>
+      <c r="AC34" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -4522,7 +4534,11 @@
       <c r="AB37" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC37" s="4" t="inlineStr"/>
+      <c r="AC37" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -5451,7 +5467,11 @@
       <c r="AB46" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC46" s="4" t="inlineStr"/>
+      <c r="AC46" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -8662,7 +8682,11 @@
       <c r="AB77" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="AC77" s="4" t="inlineStr"/>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Smedley Distinguished</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AC77"/>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 23-Sep-2026. Built 2026-09-23 23:41 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>280 days remain until 30 June 2027, when these scores become final.</t>
+          <t>276 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (99 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (158 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (189 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 9 clubs short</t>
         </is>
       </c>
     </row>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -12,7 +12,7 @@
     <sheet name="By Area" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Club Health'!$A$1:$AC$78</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'By Area'!$A$1:$I$17</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 26-Sep-2026. Built 2026-09-27 12:40 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>276 days remain until 30 June 2027, when these scores become final.</t>
+          <t>269 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (95 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (154 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (185 days) - 9 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC77"/>
+  <dimension ref="A1:AC78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1470,7 +1470,7 @@
         </is>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" s="6" t="n">
         <v>10</v>
@@ -1540,8 +1540,8 @@
       <c r="Y8" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z8" s="9" t="n">
-        <v>0</v>
+      <c r="Z8" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA8" s="10" t="n">
         <v>1</v>
@@ -1777,7 +1777,7 @@
         </is>
       </c>
       <c r="E11" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F11" s="6" t="n">
         <v>10</v>
@@ -1847,8 +1847,8 @@
       <c r="Y11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z11" s="9" t="n">
-        <v>0</v>
+      <c r="Z11" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA11" s="10" t="n">
         <v>1</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2461,8 +2461,8 @@
       <c r="Y17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" s="9" t="n">
-        <v>0</v>
+      <c r="Z17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA17" s="10" t="n">
         <v>1</v>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
       <c r="E45" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F45" s="6" t="n">
         <v>10</v>
@@ -5357,8 +5357,8 @@
       <c r="Y45" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z45" s="9" t="n">
-        <v>0</v>
+      <c r="Z45" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA45" s="10" t="n">
         <v>1</v>
@@ -5586,15 +5586,15 @@
         </is>
       </c>
       <c r="C48" s="4" t="n">
-        <v>6608731</v>
+        <v>28680764</v>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Y.O.L.O Toastmasters</t>
+          <t>Triangle Toastmasters Club</t>
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F48" s="6" t="n">
         <v>10</v>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J48" s="4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5646,38 +5646,32 @@
       <c r="S48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U48" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="V48" s="10" t="n">
-        <v>4</v>
+      <c r="T48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U48" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V48" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X48" s="10" t="n">
-        <v>6</v>
+      <c r="X48" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y48" s="9" t="n">
         <v>0</v>
       </c>
       <c r="Z48" s="10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AA48" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="AB48" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC48" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AB48" s="4" t="n"/>
+      <c r="AC48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -5687,19 +5681,19 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>61</t>
         </is>
       </c>
       <c r="C49" s="4" t="n">
-        <v>1327707</v>
+        <v>6608731</v>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>Busan Toastmasters</t>
+          <t>Y.O.L.O Toastmasters</t>
         </is>
       </c>
       <c r="E49" s="5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F49" s="6" t="n">
         <v>10</v>
@@ -5713,17 +5707,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J49" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L49" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5740,7 +5734,7 @@
         </is>
       </c>
       <c r="P49" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" s="9" t="n">
         <v>0</v>
@@ -5749,34 +5743,34 @@
         <v>0</v>
       </c>
       <c r="S49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V49" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="T49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V49" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W49" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X49" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y49" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA49" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB49" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y49" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z49" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA49" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB49" s="4" t="n">
-        <v>7</v>
       </c>
       <c r="AC49" s="4" t="inlineStr">
         <is>
@@ -5796,11 +5790,11 @@
         </is>
       </c>
       <c r="C50" s="4" t="n">
-        <v>1555924</v>
+        <v>1327707</v>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Changwon Toastmasters</t>
+          <t>Busan Toastmasters</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
@@ -5818,13 +5812,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="J50" s="4" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -5863,13 +5857,13 @@
         <v>0</v>
       </c>
       <c r="V50" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X50" s="9" t="n">
-        <v>3</v>
+      <c r="X50" s="10" t="n">
+        <v>5</v>
       </c>
       <c r="Y50" s="9" t="n">
         <v>0</v>
@@ -5881,9 +5875,13 @@
         <v>1</v>
       </c>
       <c r="AB50" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AC50" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC50" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -5897,11 +5895,11 @@
         </is>
       </c>
       <c r="C51" s="4" t="n">
-        <v>28678318</v>
+        <v>1555924</v>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Gimhae Toastmasters</t>
+          <t>Changwon Toastmasters</t>
         </is>
       </c>
       <c r="E51" s="5" t="n">
@@ -5919,17 +5917,17 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="J51" s="4" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L51" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M51" s="7" t="n">
@@ -5964,13 +5962,13 @@
         <v>0</v>
       </c>
       <c r="V51" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W51" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X51" s="10" t="n">
-        <v>7</v>
+      <c r="X51" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="Y51" s="9" t="n">
         <v>0</v>
@@ -5982,13 +5980,9 @@
         <v>1</v>
       </c>
       <c r="AB51" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC51" s="4" t="inlineStr">
-        <is>
-          <t>Select Distinguished</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AC51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -6002,15 +5996,15 @@
         </is>
       </c>
       <c r="C52" s="4" t="n">
-        <v>1895139</v>
+        <v>28678318</v>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Go-Getters Toastmasters</t>
+          <t>Gimhae Toastmasters</t>
         </is>
       </c>
       <c r="E52" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" s="6" t="n">
         <v>10</v>
@@ -6024,17 +6018,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="J52" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="K52" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L52" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M52" s="7" t="n">
@@ -6075,21 +6069,25 @@
         <v>0</v>
       </c>
       <c r="X52" s="10" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Y52" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z52" s="9" t="n">
-        <v>0</v>
+      <c r="Z52" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA52" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB52" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC52" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC52" s="4" t="inlineStr">
+        <is>
+          <t>Select Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -6103,15 +6101,15 @@
         </is>
       </c>
       <c r="C53" s="4" t="n">
-        <v>5921082</v>
+        <v>1895139</v>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Radio Drama Toastmasters Club</t>
+          <t>Go-Getters Toastmasters</t>
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F53" s="6" t="n">
         <v>10</v>
@@ -6128,10 +6126,10 @@
         <v>10</v>
       </c>
       <c r="J53" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6170,25 +6168,25 @@
         <v>0</v>
       </c>
       <c r="V53" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W53" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X53" s="10" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y53" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z53" s="10" t="n">
-        <v>1</v>
+      <c r="Z53" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="AA53" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB53" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AC53" s="4" t="inlineStr"/>
     </row>
@@ -6200,19 +6198,19 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>71</t>
         </is>
       </c>
       <c r="C54" s="4" t="n">
-        <v>7657258</v>
+        <v>5921082</v>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Gwangju Toastmasters</t>
+          <t>Radio Drama Toastmasters Club</t>
         </is>
       </c>
       <c r="E54" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F54" s="6" t="n">
         <v>10</v>
@@ -6276,20 +6274,20 @@
       <c r="W54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X54" s="9" t="n">
-        <v>3</v>
+      <c r="X54" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y54" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z54" s="9" t="n">
-        <v>0</v>
+      <c r="Z54" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA54" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB54" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="AC54" s="4" t="inlineStr"/>
     </row>
@@ -6305,15 +6303,15 @@
         </is>
       </c>
       <c r="C55" s="4" t="n">
-        <v>1305860</v>
+        <v>7657258</v>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Jinju Toastmasters</t>
+          <t>Gwangju Toastmasters</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6327,13 +6325,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J55" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6354,7 +6352,7 @@
         </is>
       </c>
       <c r="P55" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55" s="9" t="n">
         <v>0</v>
@@ -6363,40 +6361,36 @@
         <v>0</v>
       </c>
       <c r="S55" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T55" s="10" t="n">
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="T55" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V55" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X55" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y55" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA55" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB55" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="W55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X55" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="Y55" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z55" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA55" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB55" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC55" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+      <c r="AC55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -6410,15 +6404,15 @@
         </is>
       </c>
       <c r="C56" s="4" t="n">
-        <v>2541788</v>
+        <v>1305860</v>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>JNU Toastmasters</t>
+          <t>Jinju Toastmasters</t>
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6432,13 +6426,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J56" s="4" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6459,7 +6453,7 @@
         </is>
       </c>
       <c r="P56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
         <v>0</v>
@@ -6468,36 +6462,40 @@
         <v>0</v>
       </c>
       <c r="S56" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="T56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U56" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V56" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X56" s="9" t="n">
-        <v>0</v>
+      <c r="X56" s="10" t="n">
+        <v>6</v>
       </c>
       <c r="Y56" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z56" s="9" t="n">
-        <v>0</v>
+      <c r="Z56" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA56" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB56" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC56" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC56" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -6511,15 +6509,15 @@
         </is>
       </c>
       <c r="C57" s="4" t="n">
-        <v>28679972</v>
+        <v>2541788</v>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>K Culture Toastmasters</t>
+          <t>JNU Toastmasters</t>
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6533,17 +6531,17 @@
         </is>
       </c>
       <c r="I57" s="4" t="n">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="J57" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="K57" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L57" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L57" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M57" s="7" t="n">
@@ -6571,20 +6569,20 @@
       <c r="S57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T57" s="10" t="n">
-        <v>1</v>
+      <c r="T57" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="10" t="n">
-        <v>4</v>
+      <c r="V57" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="W57" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="X57" s="10" t="n">
-        <v>7</v>
+        <v>0</v>
+      </c>
+      <c r="X57" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="Y57" s="9" t="n">
         <v>0</v>
@@ -6596,35 +6594,31 @@
         <v>1</v>
       </c>
       <c r="AB57" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC57" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="AC57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C58" s="4" t="n">
-        <v>7535536</v>
+        <v>28679972</v>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Gachon Global Leaders Toastmasters</t>
+          <t>K Culture Toastmasters</t>
         </is>
       </c>
       <c r="E58" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F58" s="6" t="n">
         <v>10</v>
@@ -6638,13 +6632,13 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J58" s="4" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
@@ -6676,20 +6670,20 @@
       <c r="S58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T58" s="9" t="n">
-        <v>0</v>
+      <c r="T58" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U58" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V58" s="9" t="n">
-        <v>1</v>
+      <c r="V58" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W58" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X58" s="10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y58" s="9" t="n">
         <v>0</v>
@@ -6701,11 +6695,11 @@
         <v>1</v>
       </c>
       <c r="AB58" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="AC58" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -6721,11 +6715,11 @@
         </is>
       </c>
       <c r="C59" s="4" t="n">
-        <v>1977909</v>
+        <v>7535536</v>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Global Talents Online Toastmasters</t>
+          <t>Gachon Global Leaders Toastmasters</t>
         </is>
       </c>
       <c r="E59" s="5" t="n">
@@ -6743,13 +6737,13 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J59" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
@@ -6770,7 +6764,7 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" s="9" t="n">
         <v>0</v>
@@ -6788,13 +6782,13 @@
         <v>0</v>
       </c>
       <c r="V59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W59" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X59" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y59" s="9" t="n">
         <v>0</v>
@@ -6806,11 +6800,11 @@
         <v>1</v>
       </c>
       <c r="AB59" s="4" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AC59" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -6826,15 +6820,15 @@
         </is>
       </c>
       <c r="C60" s="4" t="n">
-        <v>7916411</v>
+        <v>1977909</v>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Jamsil Bilingual Toastmasters</t>
+          <t>Global Talents Online Toastmasters</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F60" s="6" t="n">
         <v>10</v>
@@ -6848,17 +6842,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="J60" s="4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L60" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L60" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6875,7 +6869,7 @@
         </is>
       </c>
       <c r="P60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="9" t="n">
         <v>0</v>
@@ -6893,27 +6887,31 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X60" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y60" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="Z60" s="9" t="n">
-        <v>0</v>
+      <c r="Z60" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="AA60" s="10" t="n">
         <v>1</v>
       </c>
       <c r="AB60" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC60" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC60" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -6927,11 +6925,11 @@
         </is>
       </c>
       <c r="C61" s="4" t="n">
-        <v>4049432</v>
+        <v>7916411</v>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Jamsil Brunch Toastmasters</t>
+          <t>Jamsil Bilingual Toastmasters</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
@@ -6949,17 +6947,17 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="J61" s="4" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L61" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L61" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M61" s="7" t="n">
@@ -6994,13 +6992,13 @@
         <v>0</v>
       </c>
       <c r="V61" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="W61" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X61" s="10" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y61" s="9" t="n">
         <v>0</v>
@@ -7012,13 +7010,9 @@
         <v>1</v>
       </c>
       <c r="AB61" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC61" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -7032,11 +7026,11 @@
         </is>
       </c>
       <c r="C62" s="4" t="n">
-        <v>28677084</v>
+        <v>4049432</v>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Pyeongchon Toastmasters</t>
+          <t>Jamsil Brunch Toastmasters</t>
         </is>
       </c>
       <c r="E62" s="5" t="n">
@@ -7054,17 +7048,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="J62" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L62" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L62" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -7099,7 +7093,7 @@
         <v>0</v>
       </c>
       <c r="V62" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7117,9 +7111,13 @@
         <v>1</v>
       </c>
       <c r="AB62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC62" s="4" t="inlineStr"/>
+        <v>7</v>
+      </c>
+      <c r="AC62" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="4" t="inlineStr">
@@ -7129,43 +7127,43 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C63" s="4" t="n">
-        <v>3281377</v>
+        <v>28677084</v>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Gangnam Morning Toastmasters</t>
+          <t>Pyeongchon Toastmasters</t>
         </is>
       </c>
       <c r="E63" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G63" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H63" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I63" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="J63" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="K63" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F63" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H63" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L63" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L63" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M63" s="7" t="n">
@@ -7199,11 +7197,11 @@
       <c r="U63" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V63" s="10" t="n">
-        <v>4</v>
+      <c r="V63" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="W63" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X63" s="10" t="n">
         <v>5</v>
@@ -7218,13 +7216,9 @@
         <v>1</v>
       </c>
       <c r="AB63" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC63" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="AC63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -7238,15 +7232,15 @@
         </is>
       </c>
       <c r="C64" s="4" t="n">
-        <v>1403902</v>
+        <v>3281377</v>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>New COEX TM</t>
+          <t>Gangnam Morning Toastmasters</t>
         </is>
       </c>
       <c r="E64" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F64" s="6" t="n">
         <v>10</v>
@@ -7260,17 +7254,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="J64" s="4" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L64" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>7</v>
+      </c>
+      <c r="L64" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M64" s="7" t="n">
@@ -7304,14 +7298,14 @@
       <c r="U64" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V64" s="9" t="n">
-        <v>2</v>
+      <c r="V64" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W64" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X64" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y64" s="9" t="n">
         <v>0</v>
@@ -7343,39 +7337,39 @@
         </is>
       </c>
       <c r="C65" s="4" t="n">
-        <v>28678093</v>
+        <v>1403902</v>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Seonleung Toastmasters</t>
+          <t>New COEX TM</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G65" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="J65" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="K65" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="F65" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>Smedley</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>22</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L65" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M65" s="7" t="n">
@@ -7392,43 +7386,43 @@
         </is>
       </c>
       <c r="P65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q65" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V65" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="R65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S65" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V65" s="9" t="n">
-        <v>3</v>
-      </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X65" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y65" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA65" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB65" s="4" t="n">
         <v>5</v>
-      </c>
-      <c r="Y65" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z65" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA65" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB65" s="4" t="n">
-        <v>6</v>
       </c>
       <c r="AC65" s="4" t="inlineStr">
         <is>
@@ -7448,15 +7442,15 @@
         </is>
       </c>
       <c r="C66" s="4" t="n">
-        <v>1529131</v>
+        <v>28678093</v>
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Seoul Online Book Toastmasters</t>
+          <t>Seonleung Toastmasters</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F66" s="6" t="n">
         <v>10</v>
@@ -7470,17 +7464,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="J66" s="4" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M66" s="7" t="n">
@@ -7497,16 +7491,16 @@
         </is>
       </c>
       <c r="P66" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="Q66" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="S66" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T66" s="9" t="n">
         <v>0</v>
@@ -7515,13 +7509,13 @@
         <v>0</v>
       </c>
       <c r="V66" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W66" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X66" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y66" s="9" t="n">
         <v>0</v>
@@ -7533,7 +7527,7 @@
         <v>1</v>
       </c>
       <c r="AB66" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC66" s="4" t="inlineStr">
         <is>
@@ -7553,11 +7547,11 @@
         </is>
       </c>
       <c r="C67" s="4" t="n">
-        <v>4358011</v>
+        <v>1529131</v>
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Seoul Professional Toastmasters</t>
+          <t>Seoul Online Book Toastmasters</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
@@ -7575,10 +7569,10 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="J67" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="K67" s="4" t="n">
         <v>0</v>
@@ -7625,8 +7619,8 @@
       <c r="W67" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X67" s="9" t="n">
-        <v>3</v>
+      <c r="X67" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y67" s="9" t="n">
         <v>0</v>
@@ -7654,15 +7648,15 @@
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C68" s="4" t="n">
-        <v>4064386</v>
+        <v>4358011</v>
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Blue Ribbon Toastmasters</t>
+          <t>Seoul Professional Toastmasters</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
@@ -7680,17 +7674,17 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J68" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
         <v>0</v>
       </c>
-      <c r="L68" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+      <c r="L68" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M68" s="7" t="n">
@@ -7730,24 +7724,24 @@
       <c r="W68" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X68" s="10" t="n">
+      <c r="X68" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y68" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA68" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB68" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="Y68" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z68" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA68" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB68" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="AC68" s="4" t="inlineStr">
         <is>
-          <t>President's Distinguished</t>
+          <t>Distinguished</t>
         </is>
       </c>
     </row>
@@ -7763,15 +7757,15 @@
         </is>
       </c>
       <c r="C69" s="4" t="n">
-        <v>28679161</v>
+        <v>4064386</v>
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Bundang Korean Toastmasters Club</t>
+          <t>Blue Ribbon Toastmasters</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F69" s="6" t="n">
         <v>10</v>
@@ -7785,17 +7779,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="J69" s="4" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L69" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>0</v>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M69" s="7" t="n">
@@ -7812,7 +7806,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7823,14 +7817,14 @@
       <c r="S69" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T69" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U69" s="10" t="n">
-        <v>1</v>
+      <c r="T69" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U69" s="9" t="n">
+        <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7848,9 +7842,13 @@
         <v>1</v>
       </c>
       <c r="AB69" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC69" s="4" t="inlineStr"/>
+        <v>9</v>
+      </c>
+      <c r="AC69" s="4" t="inlineStr">
+        <is>
+          <t>President's Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="4" t="inlineStr">
@@ -7864,15 +7862,15 @@
         </is>
       </c>
       <c r="C70" s="4" t="n">
-        <v>2239775</v>
+        <v>28679161</v>
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Bundang Toastmasters</t>
+          <t>Bundang Korean Toastmasters Club</t>
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7886,17 +7884,17 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="J70" s="4" t="n">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L70" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>3</v>
+      </c>
+      <c r="L70" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M70" s="7" t="n">
@@ -7913,7 +7911,7 @@
         </is>
       </c>
       <c r="P70" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="9" t="n">
         <v>0</v>
@@ -7922,22 +7920,22 @@
         <v>0</v>
       </c>
       <c r="S70" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="T70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U70" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V70" s="10" t="n">
-        <v>4</v>
+        <v>0</v>
+      </c>
+      <c r="T70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="V70" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W70" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X70" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y70" s="9" t="n">
         <v>0</v>
@@ -7949,13 +7947,9 @@
         <v>1</v>
       </c>
       <c r="AB70" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="AC70" s="4" t="inlineStr">
-        <is>
-          <t>President's Distinguished</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="AC70" s="4" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="4" t="inlineStr">
@@ -7969,15 +7963,15 @@
         </is>
       </c>
       <c r="C71" s="4" t="n">
-        <v>5087298</v>
+        <v>2239775</v>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Pangyo Toastmasters</t>
+          <t>Bundang Toastmasters</t>
         </is>
       </c>
       <c r="E71" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F71" s="6" t="n">
         <v>10</v>
@@ -7991,13 +7985,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="J71" s="4" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8018,7 +8012,7 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="9" t="n">
         <v>0</v>
@@ -8027,22 +8021,22 @@
         <v>0</v>
       </c>
       <c r="S71" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T71" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U71" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="V71" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
+      </c>
+      <c r="T71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X71" s="10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y71" s="9" t="n">
         <v>0</v>
@@ -8074,15 +8068,15 @@
         </is>
       </c>
       <c r="C72" s="4" t="n">
-        <v>28678528</v>
+        <v>5087298</v>
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Spirited Toastmasters Club</t>
+          <t>Pangyo Toastmasters</t>
         </is>
       </c>
       <c r="E72" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F72" s="6" t="n">
         <v>10</v>
@@ -8096,13 +8090,13 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="J72" s="4" t="n">
-        <v>17</v>
-      </c>
       <c r="K72" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L72" s="4" t="inlineStr">
         <is>
@@ -8134,20 +8128,20 @@
       <c r="S72" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T72" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U72" s="9" t="n">
-        <v>0</v>
+      <c r="T72" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="V72" s="9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="W72" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X72" s="10" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y72" s="9" t="n">
         <v>0</v>
@@ -8159,11 +8153,11 @@
         <v>1</v>
       </c>
       <c r="AB72" s="4" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="AC72" s="4" t="inlineStr">
         <is>
-          <t>Distinguished</t>
+          <t>President's Distinguished</t>
         </is>
       </c>
     </row>
@@ -8175,15 +8169,15 @@
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C73" s="4" t="n">
-        <v>28676025</v>
+        <v>28678528</v>
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Dongtan Toastmasters</t>
+          <t>Spirited Toastmasters Club</t>
         </is>
       </c>
       <c r="E73" s="5" t="n">
@@ -8201,17 +8195,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J73" s="4" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L73" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M73" s="7" t="n">
@@ -8228,7 +8222,7 @@
         </is>
       </c>
       <c r="P73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q73" s="9" t="n">
         <v>0</v>
@@ -8246,13 +8240,13 @@
         <v>0</v>
       </c>
       <c r="V73" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W73" s="9" t="n">
         <v>0</v>
       </c>
       <c r="X73" s="10" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="Y73" s="9" t="n">
         <v>0</v>
@@ -8264,7 +8258,7 @@
         <v>1</v>
       </c>
       <c r="AB73" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC73" s="4" t="inlineStr">
         <is>
@@ -8284,15 +8278,15 @@
         </is>
       </c>
       <c r="C74" s="4" t="n">
-        <v>1569442</v>
+        <v>28676025</v>
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Samsung One Toastmasters (SOTM)</t>
+          <t>Dongtan Toastmasters</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F74" s="6" t="n">
         <v>10</v>
@@ -8306,13 +8300,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="J74" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8333,31 +8327,31 @@
         </is>
       </c>
       <c r="P74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U74" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V74" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q74" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="R74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T74" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="U74" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V74" s="9" t="n">
-        <v>0</v>
-      </c>
       <c r="W74" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X74" s="9" t="n">
-        <v>2</v>
+      <c r="X74" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="Y74" s="9" t="n">
         <v>0</v>
@@ -8369,9 +8363,13 @@
         <v>1</v>
       </c>
       <c r="AB74" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="AC74" s="4" t="inlineStr"/>
+        <v>5</v>
+      </c>
+      <c r="AC74" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="4" t="inlineStr">
@@ -8385,15 +8383,15 @@
         </is>
       </c>
       <c r="C75" s="4" t="n">
-        <v>28679108</v>
+        <v>1569442</v>
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Speech Engineers Toastmasters</t>
+          <t>Samsung One Toastmasters (SOTM)</t>
         </is>
       </c>
       <c r="E75" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F75" s="6" t="n">
         <v>10</v>
@@ -8407,17 +8405,17 @@
         </is>
       </c>
       <c r="I75" s="4" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J75" s="4" t="n">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="K75" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L75" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L75" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M75" s="7" t="n">
@@ -8436,8 +8434,8 @@
       <c r="P75" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="Q75" s="9" t="n">
-        <v>0</v>
+      <c r="Q75" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R75" s="9" t="n">
         <v>0</v>
@@ -8445,20 +8443,20 @@
       <c r="S75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="T75" s="9" t="n">
-        <v>0</v>
+      <c r="T75" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U75" s="9" t="n">
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="X75" s="10" t="n">
-        <v>5</v>
+      <c r="X75" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="Y75" s="9" t="n">
         <v>0</v>
@@ -8470,13 +8468,9 @@
         <v>1</v>
       </c>
       <c r="AB75" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC75" s="4" t="inlineStr">
-        <is>
-          <t>Distinguished</t>
-        </is>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="AC75" s="4" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="4" t="inlineStr">
@@ -8490,15 +8484,15 @@
         </is>
       </c>
       <c r="C76" s="4" t="n">
-        <v>1529737</v>
+        <v>28679108</v>
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Suwon Toastmasters Club</t>
+          <t>Speech Engineers Toastmasters</t>
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8512,13 +8506,13 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J76" s="4" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L76" s="4" t="inlineStr">
         <is>
@@ -8539,10 +8533,10 @@
         </is>
       </c>
       <c r="P76" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R76" s="9" t="n">
         <v>0</v>
@@ -8556,14 +8550,14 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="10" t="n">
-        <v>4</v>
+      <c r="V76" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="W76" s="9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X76" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Y76" s="9" t="n">
         <v>0</v>
@@ -8575,7 +8569,7 @@
         <v>1</v>
       </c>
       <c r="AB76" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AC76" s="4" t="inlineStr">
         <is>
@@ -8595,15 +8589,15 @@
         </is>
       </c>
       <c r="C77" s="4" t="n">
-        <v>4190187</v>
+        <v>1529737</v>
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Yeongtong Toastmasters</t>
+          <t>Suwon Toastmasters Club</t>
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8617,13 +8611,13 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J77" s="4" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L77" s="4" t="inlineStr">
         <is>
@@ -8644,52 +8638,157 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="R77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V77" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="W77" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="X77" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y77" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA77" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB77" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="AC77" s="4" t="inlineStr">
+        <is>
+          <t>Distinguished</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="4" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="n">
+        <v>4190187</v>
+      </c>
+      <c r="D78" s="4" t="inlineStr">
+        <is>
+          <t>Yeongtong Toastmasters</t>
+        </is>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="G78" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="H78" s="4" t="inlineStr">
+        <is>
+          <t>Smedley</t>
+        </is>
+      </c>
+      <c r="I78" s="4" t="n">
+        <v>28</v>
+      </c>
+      <c r="J78" s="4" t="n">
+        <v>26</v>
+      </c>
+      <c r="K78" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="Q77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="R77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="T77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V77" s="9" t="n">
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="M78" s="7" t="n">
+        <v>46446</v>
+      </c>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>Officers trained Nov-Feb</t>
+        </is>
+      </c>
+      <c r="O78" s="8" t="inlineStr">
+        <is>
+          <t>not yet</t>
+        </is>
+      </c>
+      <c r="P78" s="9" t="n">
         <v>2</v>
       </c>
-      <c r="W77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X77" s="10" t="n">
+      <c r="Q78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V78" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="W78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X78" s="10" t="n">
         <v>5</v>
       </c>
-      <c r="Y77" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA77" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB77" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC77" s="4" t="inlineStr">
+      <c r="Y78" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA78" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB78" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC78" s="4" t="inlineStr">
         <is>
           <t>Smedley Distinguished</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC77"/>
+  <autoFilter ref="A1:AC78"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -8809,7 +8908,7 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -8875,7 +8974,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -9070,16 +9169,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -9088,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -9139,7 +9238,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -9172,7 +9271,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 03-Oct-2026. Built 2026-10-04 12:23 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>269 days remain until 30 June 2027, when these scores become final.</t>
+          <t>262 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (88 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (147 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (178 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>2</v>
+        <v>-7</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>7</v>
+        <v>-3</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1072,17 +1072,17 @@
         </is>
       </c>
       <c r="I4" s="4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J4" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L4" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M4" s="7" t="n">
@@ -1177,13 +1177,13 @@
         </is>
       </c>
       <c r="I5" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J5" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="L5" s="8" t="inlineStr">
         <is>
@@ -1278,17 +1278,17 @@
         </is>
       </c>
       <c r="I6" s="4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J6" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L6" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>3</v>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M6" s="7" t="n">
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>5</v>
+        <v>-3</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -1529,7 +1529,7 @@
         <v>0</v>
       </c>
       <c r="V8" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W8" s="9" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
         </is>
       </c>
       <c r="I9" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J9" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L9" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M9" s="7" t="n">
@@ -1686,13 +1686,13 @@
         </is>
       </c>
       <c r="I10" s="4" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="J10" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>2</v>
+        <v>-9</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
@@ -1791,13 +1791,13 @@
         </is>
       </c>
       <c r="I11" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J11" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L11" s="8" t="inlineStr">
         <is>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="S11" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T11" s="10" t="n">
         <v>1</v>
@@ -1892,17 +1892,17 @@
         </is>
       </c>
       <c r="I12" s="4" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="J12" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L12" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L12" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M12" s="7" t="n">
@@ -1997,17 +1997,17 @@
         </is>
       </c>
       <c r="I13" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="J13" s="4" t="n">
         <v>25</v>
       </c>
       <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-9</v>
+      </c>
+      <c r="L13" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M13" s="7" t="n">
@@ -2098,17 +2098,17 @@
         </is>
       </c>
       <c r="I14" s="4" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J14" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L14" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L14" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M14" s="7" t="n">
@@ -2143,7 +2143,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W14" s="9" t="n">
         <v>0</v>
@@ -2203,17 +2203,17 @@
         </is>
       </c>
       <c r="I15" s="4" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="J15" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L15" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M15" s="7" t="n">
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="I16" s="4" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="J16" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L16" s="8" t="inlineStr">
         <is>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F17" s="6" t="n">
         <v>10</v>
@@ -2449,8 +2449,8 @@
       <c r="U17" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V17" s="9" t="n">
-        <v>1</v>
+      <c r="V17" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W17" s="9" t="n">
         <v>0</v>
@@ -2506,13 +2506,13 @@
         </is>
       </c>
       <c r="I18" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J18" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K18" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L18" s="8" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W18" s="9" t="n">
         <v>0</v>
@@ -2611,17 +2611,17 @@
         </is>
       </c>
       <c r="I19" s="4" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="J19" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L19" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L19" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M19" s="7" t="n">
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2716,17 +2716,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L20" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>1</v>
+      </c>
+      <c r="L20" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M20" s="7" t="n">
@@ -2760,11 +2760,11 @@
       <c r="U20" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V20" s="9" t="n">
-        <v>3</v>
+      <c r="V20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>4</v>
@@ -2821,13 +2821,13 @@
         </is>
       </c>
       <c r="I21" s="4" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="J21" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K21" s="4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L21" s="8" t="inlineStr">
         <is>
@@ -2922,17 +2922,17 @@
         </is>
       </c>
       <c r="I22" s="4" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J22" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K22" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L22" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L22" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M22" s="7" t="n">
@@ -2970,7 +2970,7 @@
         <v>4</v>
       </c>
       <c r="W22" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" s="10" t="n">
         <v>5</v>
@@ -3027,17 +3027,17 @@
         </is>
       </c>
       <c r="I23" s="4" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J23" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K23" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L23" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-2</v>
+      </c>
+      <c r="L23" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M23" s="7" t="n">
@@ -3132,13 +3132,13 @@
         </is>
       </c>
       <c r="I24" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J24" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K24" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L24" s="8" t="inlineStr">
         <is>
@@ -3233,13 +3233,13 @@
         </is>
       </c>
       <c r="I25" s="4" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J25" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K25" s="4" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="L25" s="8" t="inlineStr">
         <is>
@@ -3338,13 +3338,13 @@
         </is>
       </c>
       <c r="I26" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J26" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K26" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L26" s="8" t="inlineStr">
         <is>
@@ -3439,13 +3439,13 @@
         </is>
       </c>
       <c r="I27" s="4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J27" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L27" s="8" t="inlineStr">
         <is>
@@ -3540,13 +3540,13 @@
         </is>
       </c>
       <c r="I28" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J28" s="4" t="n">
         <v>11</v>
       </c>
       <c r="K28" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L28" s="8" t="inlineStr">
         <is>
@@ -3645,17 +3645,17 @@
         </is>
       </c>
       <c r="I29" s="4" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="J29" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K29" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L29" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M29" s="7" t="n">
@@ -3746,13 +3746,13 @@
         </is>
       </c>
       <c r="I30" s="4" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="J30" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>2</v>
+        <v>-3</v>
       </c>
       <c r="L30" s="8" t="inlineStr">
         <is>
@@ -3847,13 +3847,13 @@
         </is>
       </c>
       <c r="I31" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J31" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L31" s="8" t="inlineStr">
         <is>
@@ -3948,17 +3948,17 @@
         </is>
       </c>
       <c r="I32" s="4" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="J32" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-15</v>
+      </c>
+      <c r="L32" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M32" s="7" t="n">
@@ -4053,13 +4053,13 @@
         </is>
       </c>
       <c r="I33" s="4" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="J33" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L33" s="8" t="inlineStr">
         <is>
@@ -4158,13 +4158,13 @@
         </is>
       </c>
       <c r="I34" s="4" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="J34" s="4" t="n">
         <v>33</v>
       </c>
       <c r="K34" s="4" t="n">
-        <v>4</v>
+        <v>-1</v>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
@@ -4206,7 +4206,7 @@
         <v>4</v>
       </c>
       <c r="W34" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X34" s="10" t="n">
         <v>4</v>
@@ -4263,13 +4263,13 @@
         </is>
       </c>
       <c r="I35" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J35" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K35" s="4" t="n">
-        <v>1</v>
+        <v>-5</v>
       </c>
       <c r="L35" s="8" t="inlineStr">
         <is>
@@ -4364,17 +4364,17 @@
         </is>
       </c>
       <c r="I36" s="4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="J36" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K36" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-10</v>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M36" s="7" t="n">
@@ -4469,13 +4469,13 @@
         </is>
       </c>
       <c r="I37" s="4" t="n">
-        <v>54</v>
+        <v>42</v>
       </c>
       <c r="J37" s="4" t="n">
         <v>48</v>
       </c>
       <c r="K37" s="4" t="n">
-        <v>6</v>
+        <v>-6</v>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>4</v>
       </c>
       <c r="W37" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X37" s="10" t="n">
         <v>6</v>
@@ -4574,13 +4574,13 @@
         </is>
       </c>
       <c r="I38" s="4" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="J38" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K38" s="4" t="n">
-        <v>5</v>
+        <v>-6</v>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
@@ -4679,17 +4679,17 @@
         </is>
       </c>
       <c r="I39" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J39" s="4" t="n">
         <v>22</v>
       </c>
       <c r="K39" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L39" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M39" s="7" t="n">
@@ -4784,17 +4784,17 @@
         </is>
       </c>
       <c r="I40" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="J40" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K40" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-6</v>
+      </c>
+      <c r="L40" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M40" s="7" t="n">
@@ -4889,17 +4889,17 @@
         </is>
       </c>
       <c r="I41" s="4" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="J41" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K41" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-5</v>
+      </c>
+      <c r="L41" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M41" s="7" t="n">
@@ -4994,13 +4994,13 @@
         </is>
       </c>
       <c r="I42" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J42" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K42" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L42" s="8" t="inlineStr">
         <is>
@@ -5095,13 +5095,13 @@
         </is>
       </c>
       <c r="I43" s="4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J43" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K43" s="4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="L43" s="8" t="inlineStr">
         <is>
@@ -5140,7 +5140,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W43" s="9" t="n">
         <v>0</v>
@@ -5200,13 +5200,13 @@
         </is>
       </c>
       <c r="I44" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J44" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K44" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L44" s="8" t="inlineStr">
         <is>
@@ -5301,13 +5301,13 @@
         </is>
       </c>
       <c r="I45" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J45" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K45" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L45" s="8" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>1</v>
       </c>
       <c r="V45" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W45" s="9" t="n">
         <v>0</v>
@@ -5402,13 +5402,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>1</v>
+        <v>-3</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="I47" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J47" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K47" s="4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L47" s="8" t="inlineStr">
         <is>
@@ -5608,13 +5608,13 @@
         </is>
       </c>
       <c r="I48" s="4" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J48" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K48" s="4" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
@@ -5653,7 +5653,7 @@
         <v>0</v>
       </c>
       <c r="V48" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W48" s="9" t="n">
         <v>0</v>
@@ -5707,17 +5707,17 @@
         </is>
       </c>
       <c r="I49" s="4" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="J49" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K49" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="L49" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-3</v>
+      </c>
+      <c r="L49" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M49" s="7" t="n">
@@ -5798,7 +5798,7 @@
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F50" s="6" t="n">
         <v>10</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="I50" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J50" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K50" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L50" s="8" t="inlineStr">
         <is>
@@ -5856,11 +5856,11 @@
       <c r="U50" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V50" s="9" t="n">
-        <v>3</v>
+      <c r="V50" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W50" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X50" s="10" t="n">
         <v>5</v>
@@ -5917,13 +5917,13 @@
         </is>
       </c>
       <c r="I51" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J51" s="4" t="n">
         <v>8</v>
       </c>
       <c r="K51" s="4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L51" s="8" t="inlineStr">
         <is>
@@ -6018,17 +6018,17 @@
         </is>
       </c>
       <c r="I52" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J52" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K52" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L52" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M52" s="7" t="n">
@@ -6123,13 +6123,13 @@
         </is>
       </c>
       <c r="I53" s="4" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="J53" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="4" t="n">
-        <v>0</v>
+        <v>-3</v>
       </c>
       <c r="L53" s="8" t="inlineStr">
         <is>
@@ -6224,13 +6224,13 @@
         </is>
       </c>
       <c r="I54" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J54" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K54" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L54" s="8" t="inlineStr">
         <is>
@@ -6311,7 +6311,7 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F55" s="6" t="n">
         <v>10</v>
@@ -6325,13 +6325,13 @@
         </is>
       </c>
       <c r="I55" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J55" s="4" t="n">
         <v>9</v>
       </c>
       <c r="K55" s="4" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="L55" s="8" t="inlineStr">
         <is>
@@ -6369,8 +6369,8 @@
       <c r="U55" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V55" s="9" t="n">
-        <v>1</v>
+      <c r="V55" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W55" s="9" t="n">
         <v>0</v>
@@ -6426,13 +6426,13 @@
         </is>
       </c>
       <c r="I56" s="4" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J56" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K56" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L56" s="8" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>1</v>
       </c>
       <c r="Q56" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6517,7 +6517,7 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F57" s="6" t="n">
         <v>10</v>
@@ -6575,8 +6575,8 @@
       <c r="U57" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V57" s="9" t="n">
-        <v>0</v>
+      <c r="V57" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W57" s="9" t="n">
         <v>0</v>
@@ -6632,17 +6632,17 @@
         </is>
       </c>
       <c r="I58" s="4" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="J58" s="4" t="n">
         <v>24</v>
       </c>
       <c r="K58" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L58" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L58" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M58" s="7" t="n">
@@ -6737,17 +6737,17 @@
         </is>
       </c>
       <c r="I59" s="4" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="J59" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K59" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="L59" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L59" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M59" s="7" t="n">
@@ -6764,7 +6764,7 @@
         </is>
       </c>
       <c r="P59" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="9" t="n">
         <v>0</v>
@@ -6842,17 +6842,17 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L60" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M60" s="7" t="n">
@@ -6947,13 +6947,13 @@
         </is>
       </c>
       <c r="I61" s="4" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J61" s="4" t="n">
         <v>10</v>
       </c>
       <c r="K61" s="4" t="n">
-        <v>1</v>
+        <v>-2</v>
       </c>
       <c r="L61" s="8" t="inlineStr">
         <is>
@@ -7034,7 +7034,7 @@
         </is>
       </c>
       <c r="E62" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F62" s="6" t="n">
         <v>10</v>
@@ -7048,17 +7048,17 @@
         </is>
       </c>
       <c r="I62" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="J62" s="4" t="n">
         <v>18</v>
       </c>
       <c r="K62" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L62" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L62" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M62" s="7" t="n">
@@ -7092,8 +7092,8 @@
       <c r="U62" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V62" s="9" t="n">
-        <v>3</v>
+      <c r="V62" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W62" s="9" t="n">
         <v>0</v>
@@ -7153,13 +7153,13 @@
         </is>
       </c>
       <c r="I63" s="4" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="J63" s="4" t="n">
         <v>12</v>
       </c>
       <c r="K63" s="4" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="L63" s="8" t="inlineStr">
         <is>
@@ -7254,17 +7254,17 @@
         </is>
       </c>
       <c r="I64" s="4" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="J64" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K64" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="L64" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-1</v>
+      </c>
+      <c r="L64" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M64" s="7" t="n">
@@ -7359,13 +7359,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7464,17 +7464,17 @@
         </is>
       </c>
       <c r="I66" s="4" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="J66" s="4" t="n">
         <v>19</v>
       </c>
       <c r="K66" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L66" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L66" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M66" s="7" t="n">
@@ -7569,13 +7569,13 @@
         </is>
       </c>
       <c r="I67" s="4" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J67" s="4" t="n">
         <v>16</v>
       </c>
       <c r="K67" s="4" t="n">
-        <v>0</v>
+        <v>-7</v>
       </c>
       <c r="L67" s="8" t="inlineStr">
         <is>
@@ -7614,7 +7614,7 @@
         <v>0</v>
       </c>
       <c r="V67" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W67" s="9" t="n">
         <v>0</v>
@@ -7674,13 +7674,13 @@
         </is>
       </c>
       <c r="I68" s="4" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="J68" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K68" s="4" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="L68" s="8" t="inlineStr">
         <is>
@@ -7779,17 +7779,17 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L69" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M69" s="7" t="n">
@@ -7870,7 +7870,7 @@
         </is>
       </c>
       <c r="E70" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F70" s="6" t="n">
         <v>10</v>
@@ -7884,13 +7884,13 @@
         </is>
       </c>
       <c r="I70" s="4" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="J70" s="4" t="n">
         <v>15</v>
       </c>
       <c r="K70" s="4" t="n">
-        <v>3</v>
+        <v>-4</v>
       </c>
       <c r="L70" s="8" t="inlineStr">
         <is>
@@ -7928,8 +7928,8 @@
       <c r="U70" s="10" t="n">
         <v>1</v>
       </c>
-      <c r="V70" s="9" t="n">
-        <v>3</v>
+      <c r="V70" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W70" s="9" t="n">
         <v>0</v>
@@ -7985,13 +7985,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>5</v>
+        <v>-7</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8090,17 +8090,17 @@
         </is>
       </c>
       <c r="I72" s="4" t="n">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="J72" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K72" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L72" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-4</v>
+      </c>
+      <c r="L72" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M72" s="7" t="n">
@@ -8181,7 +8181,7 @@
         </is>
       </c>
       <c r="E73" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F73" s="6" t="n">
         <v>10</v>
@@ -8195,17 +8195,17 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L73" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>0</v>
+      </c>
+      <c r="L73" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M73" s="7" t="n">
@@ -8239,11 +8239,11 @@
       <c r="U73" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V73" s="9" t="n">
-        <v>3</v>
+      <c r="V73" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8300,13 +8300,13 @@
         </is>
       </c>
       <c r="I74" s="4" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J74" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K74" s="4" t="n">
-        <v>2</v>
+        <v>-2</v>
       </c>
       <c r="L74" s="8" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>0</v>
       </c>
       <c r="V75" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W75" s="9" t="n">
         <v>0</v>
@@ -8492,7 +8492,7 @@
         </is>
       </c>
       <c r="E76" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F76" s="6" t="n">
         <v>10</v>
@@ -8506,17 +8506,17 @@
         </is>
       </c>
       <c r="I76" s="4" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="J76" s="4" t="n">
         <v>23</v>
       </c>
       <c r="K76" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="L76" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-8</v>
+      </c>
+      <c r="L76" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M76" s="7" t="n">
@@ -8550,8 +8550,8 @@
       <c r="U76" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V76" s="9" t="n">
-        <v>3</v>
+      <c r="V76" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W76" s="9" t="n">
         <v>0</v>
@@ -8611,17 +8611,17 @@
         </is>
       </c>
       <c r="I77" s="4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J77" s="4" t="n">
         <v>14</v>
       </c>
       <c r="K77" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L77" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>4</v>
+      </c>
+      <c r="L77" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M77" s="7" t="n">
@@ -8716,17 +8716,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L78" s="4" t="inlineStr">
-        <is>
-          <t>yes</t>
+        <v>-7</v>
+      </c>
+      <c r="L78" s="8" t="inlineStr">
+        <is>
+          <t>no</t>
         </is>
       </c>
       <c r="M78" s="7" t="n">
@@ -8761,7 +8761,7 @@
         <v>0</v>
       </c>
       <c r="V78" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W78" s="9" t="n">
         <v>0</v>
@@ -8923,7 +8923,7 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
@@ -8956,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="I4" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -8974,7 +8974,7 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8</v>
+        <v>2.2</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
@@ -8989,7 +8989,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -9022,7 +9022,7 @@
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -9055,7 +9055,7 @@
         <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9088,7 +9088,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -9121,7 +9121,7 @@
         <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -9154,7 +9154,7 @@
         <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -9187,7 +9187,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -9205,7 +9205,7 @@
         <v>5</v>
       </c>
       <c r="D12" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -9220,7 +9220,7 @@
         <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -9238,7 +9238,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>1.75</v>
+        <v>2.25</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -9253,7 +9253,7 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -9271,7 +9271,7 @@
         <v>5</v>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
@@ -9286,7 +9286,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -9319,7 +9319,7 @@
         <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -9337,7 +9337,7 @@
         <v>5</v>
       </c>
       <c r="D16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -9352,7 +9352,7 @@
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -9370,7 +9370,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6</v>
+        <v>1.8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9385,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:33 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 08:39 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 10:56 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,7 +495,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 11:03 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
         </is>
       </c>
     </row>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 10-Oct-2026. Built 2026-10-11 13:06 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>262 days remain until 30 June 2027, when these scores become final.</t>
+          <t>255 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (81 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (140 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (171 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
@@ -862,13 +862,13 @@
         </is>
       </c>
       <c r="I2" s="4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J2" s="4" t="n">
         <v>27</v>
       </c>
       <c r="K2" s="4" t="n">
-        <v>-7</v>
+        <v>-6</v>
       </c>
       <c r="L2" s="4" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>0</v>
       </c>
       <c r="V2" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W2" s="9" t="n">
         <v>0</v>
@@ -953,7 +953,7 @@
         </is>
       </c>
       <c r="E3" s="5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F3" s="6" t="n">
         <v>10</v>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1014,8 +1014,8 @@
       <c r="V3" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W3" s="9" t="n">
-        <v>3</v>
+      <c r="W3" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>6</v>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="I7" s="4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J7" s="4" t="n">
         <v>29</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>4</v>
       </c>
       <c r="W7" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X7" s="10" t="n">
         <v>6</v>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L20" s="8" t="inlineStr">
         <is>
@@ -2764,7 +2764,7 @@
         <v>4</v>
       </c>
       <c r="W20" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>4</v>
@@ -3013,7 +3013,7 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F23" s="6" t="n">
         <v>10</v>
@@ -3062,8 +3062,8 @@
       <c r="R23" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="S23" s="9" t="n">
-        <v>1</v>
+      <c r="S23" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="T23" s="9" t="n">
         <v>0</v>
@@ -5402,13 +5402,13 @@
         </is>
       </c>
       <c r="I46" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J46" s="4" t="n">
         <v>28</v>
       </c>
       <c r="K46" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
@@ -5447,7 +5447,7 @@
         <v>0</v>
       </c>
       <c r="V46" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W46" s="9" t="n">
         <v>0</v>
@@ -7359,13 +7359,13 @@
         </is>
       </c>
       <c r="I65" s="4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J65" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K65" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L65" s="8" t="inlineStr">
         <is>
@@ -7404,7 +7404,7 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W65" s="9" t="n">
         <v>0</v>
@@ -7779,13 +7779,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-8</v>
+        <v>-7</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -8012,10 +8012,10 @@
         </is>
       </c>
       <c r="P71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R71" s="9" t="n">
         <v>0</v>
@@ -8702,7 +8702,7 @@
         </is>
       </c>
       <c r="E78" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F78" s="6" t="n">
         <v>10</v>
@@ -8716,17 +8716,17 @@
         </is>
       </c>
       <c r="I78" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J78" s="4" t="n">
         <v>26</v>
       </c>
       <c r="K78" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="L78" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>-5</v>
+      </c>
+      <c r="L78" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M78" s="7" t="n">
@@ -8760,11 +8760,11 @@
       <c r="U78" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="V78" s="9" t="n">
-        <v>3</v>
+      <c r="V78" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="W78" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X78" s="10" t="n">
         <v>5</v>
@@ -8875,7 +8875,7 @@
         <v>5</v>
       </c>
       <c r="D2" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
@@ -9007,7 +9007,7 @@
         <v>5</v>
       </c>
       <c r="D6" t="n">
-        <v>1.2</v>
+        <v>1.4</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>1.8</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -9385,7 +9385,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docs/d/93/inyear.xlsx
+++ b/docs/d/93/inyear.xlsx
@@ -495,14 +495,14 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Program year 2026-2027. Dashboard snapshot 17-Oct-2026. Built 2026-10-18 11:32 PDT.</t>
+          <t>Program year 2026-2027. Dashboard snapshot 24-Oct-2026. Built 2026-10-25 11:50 PDT.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>255 days remain until 30 June 2027, when these scores become final.</t>
+          <t>248 days remain until 30 June 2027, when these scores become final.</t>
         </is>
       </c>
     </row>
@@ -574,21 +574,21 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (74 days) - 1 clubs short</t>
+          <t xml:space="preserve">   Officer list on time - closes 2026-12-31 (67 days) - 1 clubs short</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (133 days) - window opens 2026-11-01</t>
+          <t xml:space="preserve">   Officers trained Nov-Feb - closes 2027-02-28 (126 days) - window opens 2026-11-01</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (164 days) - 2 clubs short</t>
+          <t xml:space="preserve">   Renewal dues on time - closes 2027-03-31 (157 days) - 2 clubs short</t>
         </is>
       </c>
     </row>
@@ -967,13 +967,13 @@
         </is>
       </c>
       <c r="I3" s="4" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J3" s="4" t="n">
         <v>37</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>-2</v>
+        <v>-1</v>
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
@@ -1015,7 +1015,7 @@
         <v>4</v>
       </c>
       <c r="W3" s="10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="X3" s="10" t="n">
         <v>6</v>
@@ -1406,7 +1406,7 @@
         </is>
       </c>
       <c r="P7" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q7" s="9" t="n">
         <v>0</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="I8" s="4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J8" s="4" t="n">
         <v>13</v>
       </c>
       <c r="K8" s="4" t="n">
-        <v>-3</v>
+        <v>-2</v>
       </c>
       <c r="L8" s="8" t="inlineStr">
         <is>
@@ -2084,7 +2084,7 @@
         </is>
       </c>
       <c r="E14" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F14" s="6" t="n">
         <v>10</v>
@@ -2136,8 +2136,8 @@
       <c r="S14" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="T14" s="9" t="n">
-        <v>0</v>
+      <c r="T14" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="U14" s="9" t="n">
         <v>0</v>
@@ -2702,7 +2702,7 @@
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F20" s="6" t="n">
         <v>10</v>
@@ -2716,17 +2716,17 @@
         </is>
       </c>
       <c r="I20" s="4" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="L20" s="8" t="inlineStr">
-        <is>
-          <t>no</t>
+        <v>4</v>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
         </is>
       </c>
       <c r="M20" s="7" t="n">
@@ -2763,8 +2763,8 @@
       <c r="V20" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="W20" s="9" t="n">
-        <v>3</v>
+      <c r="W20" s="10" t="n">
+        <v>4</v>
       </c>
       <c r="X20" s="10" t="n">
         <v>4</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="P41" s="9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Q41" s="9" t="n">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         </is>
       </c>
       <c r="E56" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F56" s="6" t="n">
         <v>10</v>
@@ -6455,8 +6455,8 @@
       <c r="P56" s="9" t="n">
         <v>1</v>
       </c>
-      <c r="Q56" s="9" t="n">
-        <v>1</v>
+      <c r="Q56" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R56" s="9" t="n">
         <v>0</v>
@@ -6842,13 +6842,13 @@
         </is>
       </c>
       <c r="I60" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J60" s="4" t="n">
         <v>20</v>
       </c>
       <c r="K60" s="4" t="n">
-        <v>-4</v>
+        <v>-3</v>
       </c>
       <c r="L60" s="8" t="inlineStr">
         <is>
@@ -6887,7 +6887,7 @@
         <v>0</v>
       </c>
       <c r="V60" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W60" s="9" t="n">
         <v>0</v>
@@ -7779,13 +7779,13 @@
         </is>
       </c>
       <c r="I69" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J69" s="4" t="n">
         <v>21</v>
       </c>
       <c r="K69" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L69" s="8" t="inlineStr">
         <is>
@@ -7806,7 +7806,7 @@
         </is>
       </c>
       <c r="P69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="9" t="n">
         <v>0</v>
@@ -7824,7 +7824,7 @@
         <v>0</v>
       </c>
       <c r="V69" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W69" s="9" t="n">
         <v>0</v>
@@ -7985,13 +7985,13 @@
         </is>
       </c>
       <c r="I71" s="4" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J71" s="4" t="n">
         <v>32</v>
       </c>
       <c r="K71" s="4" t="n">
-        <v>-7</v>
+        <v>-5</v>
       </c>
       <c r="L71" s="4" t="inlineStr">
         <is>
@@ -8033,7 +8033,7 @@
         <v>4</v>
       </c>
       <c r="W71" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="X71" s="10" t="n">
         <v>6</v>
@@ -8195,13 +8195,13 @@
         </is>
       </c>
       <c r="I73" s="4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J73" s="4" t="n">
         <v>17</v>
       </c>
       <c r="K73" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L73" s="8" t="inlineStr">
         <is>
@@ -8243,7 +8243,7 @@
         <v>4</v>
       </c>
       <c r="W73" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="X73" s="10" t="n">
         <v>6</v>
@@ -8597,7 +8597,7 @@
         </is>
       </c>
       <c r="E77" s="5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F77" s="6" t="n">
         <v>10</v>
@@ -8638,13 +8638,13 @@
         </is>
       </c>
       <c r="P77" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q77" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
+      </c>
+      <c r="Q77" s="10" t="n">
+        <v>2</v>
       </c>
       <c r="R77" s="9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S77" s="9" t="n">
         <v>0</v>
@@ -8941,7 +8941,7 @@
         <v>5</v>
       </c>
       <c r="D4" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
@@ -8974,13 +8974,13 @@
         <v>5</v>
       </c>
       <c r="D5" t="n">
-        <v>2.2</v>
+        <v>2.4</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -8989,7 +8989,7 @@
         <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -9238,7 +9238,7 @@
         <v>4</v>
       </c>
       <c r="D13" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
@@ -9370,7 +9370,7 @@
         <v>5</v>
       </c>
       <c r="D17" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
